--- a/backend/data/financials_by_company/1304.SR.xlsx
+++ b/backend/data/financials_by_company/1304.SR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,214 +682,116 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1070137.125057</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.132188</v>
-      </c>
-      <c r="D2" t="n">
-        <v>187351651</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8095574</v>
-      </c>
-      <c r="F2" t="n">
-        <v>8095574</v>
-      </c>
-      <c r="G2" t="n">
-        <v>70800717</v>
-      </c>
-      <c r="H2" t="n">
-        <v>48047261</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1732693033</v>
-      </c>
-      <c r="J2" t="n">
-        <v>195447225</v>
-      </c>
-      <c r="K2" t="n">
-        <v>147399964</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-66420140</v>
-      </c>
-      <c r="M2" t="n">
-        <v>66453667</v>
-      </c>
-      <c r="N2" t="n">
-        <v>431894</v>
-      </c>
-      <c r="O2" t="n">
-        <v>63775280.125057</v>
-      </c>
-      <c r="P2" t="n">
-        <v>70800717</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1817953614</v>
-      </c>
-      <c r="R2" t="n">
-        <v>138637780</v>
-      </c>
-      <c r="S2" t="n">
-        <v>50800000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>50800000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W2" t="n">
-        <v>70800717</v>
-      </c>
-      <c r="X2" t="n">
-        <v>70800717</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>70800717</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>554543</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>70246174</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>70246174</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>10700123</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>80946297</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-4591</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6083671</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>919</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-6084590</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-66420140</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>398367</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>66453667</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>431894</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>138637780</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>85260581</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>3983006</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>870683</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>3112323</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>36168125</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>26615841</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9552284</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>223898361</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1732693033</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1956591394</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1956591394</v>
-      </c>
+        <v>44469</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>8603495</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45199</v>
+        <v>44834</v>
       </c>
       <c r="B3" t="n">
-        <v>441733.6</v>
+        <v>552537.6</v>
       </c>
       <c r="C3" t="n">
         <v>0.2</v>
       </c>
       <c r="D3" t="n">
-        <v>-45110229</v>
+        <v>66458308</v>
       </c>
       <c r="E3" t="n">
-        <v>2208668</v>
+        <v>2762688</v>
       </c>
       <c r="F3" t="n">
-        <v>2208668</v>
+        <v>2762688</v>
       </c>
       <c r="G3" t="n">
-        <v>-130142311</v>
+        <v>-26655991</v>
       </c>
       <c r="H3" t="n">
-        <v>48979733</v>
+        <v>47025307</v>
       </c>
       <c r="I3" t="n">
-        <v>1587952499</v>
+        <v>1386818845</v>
       </c>
       <c r="J3" t="n">
-        <v>-42901561</v>
+        <v>69220996</v>
       </c>
       <c r="K3" t="n">
-        <v>-91881294</v>
+        <v>22195689</v>
       </c>
       <c r="L3" t="n">
-        <v>-68955249</v>
+        <v>-24907807</v>
       </c>
       <c r="M3" t="n">
-        <v>68705167</v>
+        <v>25842009</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1168185</v>
       </c>
       <c r="O3" t="n">
-        <v>-131909245.4</v>
+        <v>-28866141.4</v>
       </c>
       <c r="P3" t="n">
-        <v>-130142311</v>
+        <v>-26655991</v>
       </c>
       <c r="Q3" t="n">
-        <v>1653473945</v>
+        <v>1446710020</v>
       </c>
       <c r="R3" t="n">
-        <v>-95432612</v>
+        <v>12509260</v>
       </c>
       <c r="S3" t="n">
         <v>50800000</v>
@@ -898,156 +800,154 @@
         <v>50800000</v>
       </c>
       <c r="U3" t="n">
-        <v>-2.56</v>
+        <v>-0.52</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.56</v>
+        <v>-0.52</v>
       </c>
       <c r="W3" t="n">
-        <v>-130142311</v>
+        <v>-26655991</v>
       </c>
       <c r="X3" t="n">
-        <v>-130142311</v>
+        <v>-26655991</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-130142311</v>
+        <v>-26655991</v>
       </c>
       <c r="AA3" t="n">
-        <v>35002052</v>
+        <v>-9642918</v>
       </c>
       <c r="AB3" t="n">
-        <v>-165144363</v>
+        <v>-17013073</v>
       </c>
       <c r="AC3" t="n">
-        <v>-165144363</v>
+        <v>-17013073</v>
       </c>
       <c r="AD3" t="n">
-        <v>4557902</v>
+        <v>13366753</v>
       </c>
       <c r="AE3" t="n">
-        <v>-160586461</v>
+        <v>-3646320</v>
       </c>
       <c r="AF3" t="n">
-        <v>98174</v>
+        <v>232812</v>
       </c>
       <c r="AG3" t="n">
-        <v>309667</v>
+        <v>-12384</v>
       </c>
       <c r="AH3" t="n">
-        <v>-185600</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-124067</v>
-      </c>
+        <v>12384</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>-68955249</v>
+        <v>-24907807</v>
       </c>
       <c r="AK3" t="n">
-        <v>250082</v>
+        <v>233983</v>
       </c>
       <c r="AL3" t="n">
-        <v>68705167</v>
+        <v>25842009</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1168185</v>
       </c>
       <c r="AN3" t="n">
-        <v>-93940224</v>
+        <v>18265987</v>
       </c>
       <c r="AO3" t="n">
-        <v>65521446</v>
+        <v>59891175</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1492388</v>
+        <v>-5756727</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4272876</v>
+        <v>4649230</v>
       </c>
       <c r="AR3" t="n">
-        <v>859500</v>
+        <v>835584</v>
       </c>
       <c r="AS3" t="n">
-        <v>3413376</v>
+        <v>3813646</v>
       </c>
       <c r="AT3" t="n">
-        <v>22223005</v>
+        <v>18810768</v>
       </c>
       <c r="AU3" t="n">
-        <v>14837301</v>
+        <v>11830457</v>
       </c>
       <c r="AV3" t="n">
-        <v>7385704</v>
+        <v>6980311</v>
       </c>
       <c r="AW3" t="n">
-        <v>-28418778</v>
+        <v>78157162</v>
       </c>
       <c r="AX3" t="n">
-        <v>1587952499</v>
+        <v>1386818845</v>
       </c>
       <c r="AY3" t="n">
-        <v>1559533721</v>
+        <v>1464976007</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1559533721</v>
+        <v>1464976007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44834</v>
+        <v>45199</v>
       </c>
       <c r="B4" t="n">
-        <v>552537.6</v>
+        <v>441733.6</v>
       </c>
       <c r="C4" t="n">
         <v>0.2</v>
       </c>
       <c r="D4" t="n">
-        <v>66458308</v>
+        <v>-45110229</v>
       </c>
       <c r="E4" t="n">
-        <v>2762688</v>
+        <v>2208668</v>
       </c>
       <c r="F4" t="n">
-        <v>2762688</v>
+        <v>2208668</v>
       </c>
       <c r="G4" t="n">
-        <v>-26655991</v>
+        <v>-130142311</v>
       </c>
       <c r="H4" t="n">
-        <v>47025307</v>
+        <v>48979733</v>
       </c>
       <c r="I4" t="n">
-        <v>1386818845</v>
+        <v>1587952499</v>
       </c>
       <c r="J4" t="n">
-        <v>69220996</v>
+        <v>-42901561</v>
       </c>
       <c r="K4" t="n">
-        <v>22195689</v>
+        <v>-91881294</v>
       </c>
       <c r="L4" t="n">
-        <v>-24907807</v>
+        <v>-68955249</v>
       </c>
       <c r="M4" t="n">
-        <v>25842009</v>
+        <v>68705167</v>
       </c>
       <c r="N4" t="n">
-        <v>1168185</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-28866141.4</v>
+        <v>-131909245.4</v>
       </c>
       <c r="P4" t="n">
-        <v>-26655991</v>
+        <v>-130142311</v>
       </c>
       <c r="Q4" t="n">
-        <v>1446710020</v>
+        <v>1653473945</v>
       </c>
       <c r="R4" t="n">
-        <v>12509260</v>
+        <v>-95432612</v>
       </c>
       <c r="S4" t="n">
         <v>50800000</v>
@@ -1056,154 +956,156 @@
         <v>50800000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.52</v>
+        <v>-2.56</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.52</v>
+        <v>-2.56</v>
       </c>
       <c r="W4" t="n">
-        <v>-26655991</v>
+        <v>-130142311</v>
       </c>
       <c r="X4" t="n">
-        <v>-26655991</v>
+        <v>-130142311</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-26655991</v>
+        <v>-130142311</v>
       </c>
       <c r="AA4" t="n">
-        <v>-9642918</v>
+        <v>35002052</v>
       </c>
       <c r="AB4" t="n">
-        <v>-17013073</v>
+        <v>-165144363</v>
       </c>
       <c r="AC4" t="n">
-        <v>-17013073</v>
+        <v>-165144363</v>
       </c>
       <c r="AD4" t="n">
-        <v>13366753</v>
+        <v>4557902</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3646320</v>
+        <v>-160586461</v>
       </c>
       <c r="AF4" t="n">
-        <v>232812</v>
+        <v>98174</v>
       </c>
       <c r="AG4" t="n">
-        <v>-12384</v>
+        <v>309667</v>
       </c>
       <c r="AH4" t="n">
-        <v>12384</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>-185600</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-124067</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-24907807</v>
+        <v>-68955249</v>
       </c>
       <c r="AK4" t="n">
-        <v>233983</v>
+        <v>250082</v>
       </c>
       <c r="AL4" t="n">
-        <v>25842009</v>
+        <v>68705167</v>
       </c>
       <c r="AM4" t="n">
-        <v>1168185</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>18265987</v>
+        <v>-93940224</v>
       </c>
       <c r="AO4" t="n">
-        <v>59891175</v>
+        <v>65521446</v>
       </c>
       <c r="AP4" t="n">
-        <v>-5756727</v>
+        <v>-1492388</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4649230</v>
+        <v>4272876</v>
       </c>
       <c r="AR4" t="n">
-        <v>835584</v>
+        <v>859500</v>
       </c>
       <c r="AS4" t="n">
-        <v>3813646</v>
+        <v>3413376</v>
       </c>
       <c r="AT4" t="n">
-        <v>18810768</v>
+        <v>22223005</v>
       </c>
       <c r="AU4" t="n">
-        <v>11830457</v>
+        <v>14837301</v>
       </c>
       <c r="AV4" t="n">
-        <v>6980311</v>
+        <v>7385704</v>
       </c>
       <c r="AW4" t="n">
-        <v>78157162</v>
+        <v>-28418778</v>
       </c>
       <c r="AX4" t="n">
-        <v>1386818845</v>
+        <v>1587952499</v>
       </c>
       <c r="AY4" t="n">
-        <v>1464976007</v>
+        <v>1559533721</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1464976007</v>
+        <v>1559533721</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="B5" t="n">
-        <v>77548.83300499999</v>
+        <v>1070137.125057</v>
       </c>
       <c r="C5" t="n">
-        <v>0.090699</v>
+        <v>0.132188</v>
       </c>
       <c r="D5" t="n">
-        <v>326857109</v>
+        <v>187351651</v>
       </c>
       <c r="E5" t="n">
-        <v>855014</v>
+        <v>8095574</v>
       </c>
       <c r="F5" t="n">
-        <v>855014</v>
+        <v>8095574</v>
       </c>
       <c r="G5" t="n">
-        <v>207831707</v>
+        <v>70800717</v>
       </c>
       <c r="H5" t="n">
-        <v>45696195</v>
+        <v>48047261</v>
       </c>
       <c r="I5" t="n">
-        <v>1254854073</v>
+        <v>1732693033</v>
       </c>
       <c r="J5" t="n">
-        <v>327712123</v>
+        <v>195447225</v>
       </c>
       <c r="K5" t="n">
-        <v>282015928</v>
+        <v>147399964</v>
       </c>
       <c r="L5" t="n">
-        <v>-13183242</v>
+        <v>-66420140</v>
       </c>
       <c r="M5" t="n">
-        <v>13080816</v>
+        <v>66453667</v>
       </c>
       <c r="N5" t="n">
-        <v>126968</v>
+        <v>431894</v>
       </c>
       <c r="O5" t="n">
-        <v>207054241.833005</v>
+        <v>63775280.125057</v>
       </c>
       <c r="P5" t="n">
-        <v>207831707</v>
+        <v>70800717</v>
       </c>
       <c r="Q5" t="n">
-        <v>1338727662</v>
+        <v>1817953619</v>
       </c>
       <c r="R5" t="n">
-        <v>288903423</v>
+        <v>138637780</v>
       </c>
       <c r="S5" t="n">
         <v>50800000</v>
@@ -1212,98 +1114,254 @@
         <v>50800000</v>
       </c>
       <c r="U5" t="n">
-        <v>4.09</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>4.09</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>207831707</v>
+        <v>70800717</v>
       </c>
       <c r="X5" t="n">
-        <v>207831707</v>
+        <v>70800717</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>207831707</v>
+        <v>70800717</v>
       </c>
       <c r="AA5" t="n">
-        <v>-36711285</v>
+        <v>554543</v>
       </c>
       <c r="AB5" t="n">
-        <v>244542992</v>
+        <v>70246174</v>
       </c>
       <c r="AC5" t="n">
-        <v>244542992</v>
+        <v>70246174</v>
       </c>
       <c r="AD5" t="n">
-        <v>24392120</v>
+        <v>10700123</v>
       </c>
       <c r="AE5" t="n">
-        <v>268935112</v>
+        <v>80946297</v>
       </c>
       <c r="AF5" t="n">
-        <v>815510</v>
+        <v>-4591</v>
       </c>
       <c r="AG5" t="n">
-        <v>461900</v>
+        <v>6083671</v>
       </c>
       <c r="AH5" t="n">
-        <v>-461900</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>919</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-6084590</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>-13183242</v>
+        <v>-66420140</v>
       </c>
       <c r="AK5" t="n">
-        <v>229394</v>
+        <v>398367</v>
       </c>
       <c r="AL5" t="n">
-        <v>13080816</v>
+        <v>66453667</v>
       </c>
       <c r="AM5" t="n">
-        <v>126968</v>
+        <v>431894</v>
       </c>
       <c r="AN5" t="n">
-        <v>280299928</v>
+        <v>138637775</v>
       </c>
       <c r="AO5" t="n">
-        <v>83873589</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>8603495</v>
-      </c>
+        <v>85260586</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>4229805</v>
+        <v>3983006</v>
       </c>
       <c r="AR5" t="n">
-        <v>835224</v>
+        <v>870683</v>
       </c>
       <c r="AS5" t="n">
-        <v>3394581</v>
+        <v>3112323</v>
       </c>
       <c r="AT5" t="n">
-        <v>24426306</v>
+        <v>36168130</v>
       </c>
       <c r="AU5" t="n">
-        <v>17687457</v>
+        <v>26523965</v>
       </c>
       <c r="AV5" t="n">
-        <v>6738849</v>
+        <v>9644165</v>
       </c>
       <c r="AW5" t="n">
-        <v>364173517</v>
+        <v>223898361</v>
       </c>
       <c r="AX5" t="n">
-        <v>1254854073</v>
+        <v>1732693033</v>
       </c>
       <c r="AY5" t="n">
-        <v>1619027590</v>
+        <v>1956591394</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1619027590</v>
+        <v>1956591394</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>952.028225</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="D6" t="n">
+        <v>158592497</v>
+      </c>
+      <c r="E6" t="n">
+        <v>680037</v>
+      </c>
+      <c r="F6" t="n">
+        <v>680037</v>
+      </c>
+      <c r="G6" t="n">
+        <v>59687481</v>
+      </c>
+      <c r="H6" t="n">
+        <v>47463212</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1677573329</v>
+      </c>
+      <c r="J6" t="n">
+        <v>159272534</v>
+      </c>
+      <c r="K6" t="n">
+        <v>111809322</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-58907358</v>
+      </c>
+      <c r="M6" t="n">
+        <v>55814364</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>59008396.028225</v>
+      </c>
+      <c r="P6" t="n">
+        <v>59687481</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1765019039</v>
+      </c>
+      <c r="R6" t="n">
+        <v>113564581</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>50800000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>59687481</v>
+      </c>
+      <c r="X6" t="n">
+        <v>59687481</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>59687481</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3770914</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>55916567</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>55916567</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>78391</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>55994958</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>57874</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-644</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>644</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-58907358</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3092994</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55814364</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>113564580</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>87445710</v>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="n">
+        <v>3385040</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>886506</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2498534</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>33689761</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>22557162</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11132599</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>201010290</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1677573329</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1878583619</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1878583619</v>
       </c>
     </row>
   </sheetData>
@@ -1317,7 +1375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,210 +1714,98 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B2" t="n">
-        <v>50800000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>50800000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>779037044</v>
-      </c>
-      <c r="E2" t="n">
-        <v>878260825</v>
-      </c>
-      <c r="F2" t="n">
-        <v>585812560</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1439137096</v>
-      </c>
-      <c r="H2" t="n">
-        <v>266297093</v>
-      </c>
-      <c r="I2" t="n">
-        <v>585812560</v>
-      </c>
-      <c r="J2" t="n">
-        <v>28204976</v>
-      </c>
-      <c r="K2" t="n">
-        <v>589081247</v>
-      </c>
-      <c r="L2" t="n">
-        <v>696259288</v>
-      </c>
-      <c r="M2" t="n">
-        <v>690965614</v>
-      </c>
-      <c r="N2" t="n">
-        <v>101884367</v>
-      </c>
-      <c r="O2" t="n">
-        <v>589081247</v>
-      </c>
-      <c r="P2" t="n">
-        <v>81081247</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>508000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>508000000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1093545933</v>
-      </c>
-      <c r="T2" t="n">
-        <v>190872900</v>
-      </c>
+        <v>44469</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="n">
-        <v>45481000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>131935623</v>
-      </c>
-      <c r="X2" t="n">
-        <v>24757582</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>107178041</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13456277</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>902673033</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16653621</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>746325202</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3447394</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>742877808</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8026244</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>95967155</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>818759</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>567562</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12109782</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>82471052</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1784511547</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>615541421</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3268687</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3268687</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>612272734</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-584087963</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1196360697</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>197464624</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>46636180</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>567019647</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>371975521</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13264725</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1168970126</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>15523871</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>679773657</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-16707252</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>25455313</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>278312192</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>29307969</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>363405435</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>698221</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>400865251</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-9926480</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>410791731</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>72109126</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1090321</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>71018805</v>
-      </c>
-      <c r="BO2" t="inlineStr"/>
-      <c r="BP2" t="n">
-        <v>71018805</v>
-      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>5807780</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45199</v>
+        <v>44834</v>
       </c>
       <c r="B3" t="n">
         <v>50800000</v>
@@ -1868,43 +1814,43 @@
         <v>50800000</v>
       </c>
       <c r="D3" t="n">
-        <v>879350643</v>
+        <v>817929231</v>
       </c>
       <c r="E3" t="n">
-        <v>933866266</v>
+        <v>920110656</v>
       </c>
       <c r="F3" t="n">
-        <v>513938807</v>
+        <v>641546178</v>
       </c>
       <c r="G3" t="n">
-        <v>1421297035</v>
+        <v>1532803278</v>
       </c>
       <c r="H3" t="n">
-        <v>151860830</v>
+        <v>326228051</v>
       </c>
       <c r="I3" t="n">
-        <v>513938807</v>
+        <v>641546178</v>
       </c>
       <c r="J3" t="n">
-        <v>30716452</v>
+        <v>33849454</v>
       </c>
       <c r="K3" t="n">
-        <v>518147221</v>
+        <v>646542076</v>
       </c>
       <c r="L3" t="n">
-        <v>598366812</v>
+        <v>649042076</v>
       </c>
       <c r="M3" t="n">
-        <v>620361935</v>
+        <v>783837978</v>
       </c>
       <c r="N3" t="n">
-        <v>102214714</v>
+        <v>137295902</v>
       </c>
       <c r="O3" t="n">
-        <v>518147221</v>
+        <v>646542076</v>
       </c>
       <c r="P3" t="n">
-        <v>-19050839</v>
+        <v>49344016</v>
       </c>
       <c r="Q3" t="n">
         <v>508000000</v>
@@ -1913,95 +1859,89 @@
         <v>508000000</v>
       </c>
       <c r="S3" t="n">
-        <v>1170531348</v>
+        <v>1135592305</v>
       </c>
       <c r="T3" t="n">
-        <v>162088754</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-1</v>
-      </c>
+        <v>83852404</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>40375596</v>
+        <v>38119601</v>
       </c>
       <c r="W3" t="n">
-        <v>108655248</v>
+        <v>33799725</v>
       </c>
       <c r="X3" t="n">
-        <v>28435657</v>
+        <v>31299725</v>
       </c>
       <c r="Y3" t="n">
-        <v>80219591</v>
+        <v>2500000</v>
       </c>
       <c r="Z3" t="n">
-        <v>13057910</v>
+        <v>11933078</v>
       </c>
       <c r="AA3" t="n">
-        <v>1008442594</v>
+        <v>1051739901</v>
       </c>
       <c r="AB3" t="n">
-        <v>25394386</v>
+        <v>29282285</v>
       </c>
       <c r="AC3" t="n">
-        <v>825211018</v>
+        <v>886310931</v>
       </c>
       <c r="AD3" t="n">
-        <v>2280795</v>
+        <v>2549729</v>
       </c>
       <c r="AE3" t="n">
-        <v>822930223</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>7563368</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>883761202</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="n">
+        <v>1492388</v>
+      </c>
       <c r="AH3" t="n">
-        <v>101723691</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>818758</v>
-      </c>
+        <v>49735352</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>567852</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>12691380</v>
-      </c>
+        <v>568881</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>87645701</v>
+        <v>49166471</v>
       </c>
       <c r="AM3" t="n">
-        <v>1790893283</v>
+        <v>1919430283</v>
       </c>
       <c r="AN3" t="n">
-        <v>630589859</v>
+        <v>541462331</v>
       </c>
       <c r="AO3" t="n">
-        <v>4208414</v>
+        <v>4995898</v>
       </c>
       <c r="AP3" t="n">
-        <v>4208414</v>
+        <v>4995898</v>
       </c>
       <c r="AQ3" t="n">
-        <v>626381445</v>
+        <v>536466433</v>
       </c>
       <c r="AR3" t="n">
-        <v>-544667547</v>
+        <v>-499566570</v>
       </c>
       <c r="AS3" t="n">
-        <v>1171048992</v>
+        <v>1036033003</v>
       </c>
       <c r="AT3" t="n">
-        <v>197330308</v>
+        <v>75569152</v>
       </c>
       <c r="AU3" t="n">
-        <v>47223106</v>
+        <v>47694258</v>
       </c>
       <c r="AV3" t="n">
-        <v>545322135</v>
+        <v>534369413</v>
       </c>
       <c r="AW3" t="n">
-        <v>367908718</v>
+        <v>365135455</v>
       </c>
       <c r="AX3" t="n">
         <v>13264725</v>
@@ -2010,60 +1950,58 @@
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1160303424</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>26212564</v>
-      </c>
+        <v>1377967952</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>780814766</v>
+        <v>939782509</v>
       </c>
       <c r="BC3" t="n">
-        <v>-21435706</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>13185518</v>
-      </c>
+        <v>-74007285</v>
+      </c>
+      <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="n">
-        <v>196060064</v>
+        <v>125779426</v>
       </c>
       <c r="BF3" t="n">
-        <v>24179061</v>
+        <v>49473576</v>
       </c>
       <c r="BG3" t="n">
-        <v>568825829</v>
+        <v>838536792</v>
       </c>
       <c r="BH3" t="n">
-        <v>617478</v>
+        <v>15510172</v>
       </c>
       <c r="BI3" t="n">
-        <v>326862117</v>
+        <v>352242535</v>
       </c>
       <c r="BJ3" t="n">
         <v>-9926480</v>
       </c>
       <c r="BK3" t="n">
-        <v>336788597</v>
+        <v>362169015</v>
       </c>
       <c r="BL3" t="n">
-        <v>25796499</v>
+        <v>70432736</v>
       </c>
       <c r="BM3" t="n">
-        <v>1997328</v>
+        <v>2100765</v>
       </c>
       <c r="BN3" t="n">
-        <v>23799171</v>
+        <v>68331971</v>
       </c>
       <c r="BO3" t="n">
-        <v>565497</v>
+        <v>180000</v>
       </c>
       <c r="BP3" t="n">
-        <v>23799171</v>
-      </c>
+        <v>68151971</v>
+      </c>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44834</v>
+        <v>45199</v>
       </c>
       <c r="B4" t="n">
         <v>50800000</v>
@@ -2072,43 +2010,43 @@
         <v>50800000</v>
       </c>
       <c r="D4" t="n">
-        <v>817929231</v>
+        <v>879350643</v>
       </c>
       <c r="E4" t="n">
-        <v>920110656</v>
+        <v>933866266</v>
       </c>
       <c r="F4" t="n">
-        <v>641546178</v>
+        <v>513938807</v>
       </c>
       <c r="G4" t="n">
-        <v>1532803278</v>
+        <v>1421297035</v>
       </c>
       <c r="H4" t="n">
-        <v>326228051</v>
+        <v>151860830</v>
       </c>
       <c r="I4" t="n">
-        <v>641546178</v>
+        <v>513938807</v>
       </c>
       <c r="J4" t="n">
-        <v>33849454</v>
+        <v>30716452</v>
       </c>
       <c r="K4" t="n">
-        <v>646542076</v>
+        <v>518147221</v>
       </c>
       <c r="L4" t="n">
-        <v>649042076</v>
+        <v>598366812</v>
       </c>
       <c r="M4" t="n">
-        <v>783837978</v>
+        <v>620361935</v>
       </c>
       <c r="N4" t="n">
-        <v>137295902</v>
+        <v>102214714</v>
       </c>
       <c r="O4" t="n">
-        <v>646542076</v>
+        <v>518147221</v>
       </c>
       <c r="P4" t="n">
-        <v>49344016</v>
+        <v>-19050839</v>
       </c>
       <c r="Q4" t="n">
         <v>508000000</v>
@@ -2117,89 +2055,95 @@
         <v>508000000</v>
       </c>
       <c r="S4" t="n">
-        <v>1135592305</v>
+        <v>1170531348</v>
       </c>
       <c r="T4" t="n">
-        <v>83852404</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>162088754</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-1</v>
+      </c>
       <c r="V4" t="n">
-        <v>38119601</v>
+        <v>40375596</v>
       </c>
       <c r="W4" t="n">
-        <v>33799725</v>
+        <v>108655248</v>
       </c>
       <c r="X4" t="n">
-        <v>31299725</v>
+        <v>28435657</v>
       </c>
       <c r="Y4" t="n">
-        <v>2500000</v>
+        <v>80219591</v>
       </c>
       <c r="Z4" t="n">
-        <v>11933078</v>
+        <v>13057910</v>
       </c>
       <c r="AA4" t="n">
-        <v>1051739901</v>
+        <v>1008442594</v>
       </c>
       <c r="AB4" t="n">
-        <v>29282285</v>
+        <v>25394386</v>
       </c>
       <c r="AC4" t="n">
-        <v>886310931</v>
+        <v>825211018</v>
       </c>
       <c r="AD4" t="n">
-        <v>2549729</v>
+        <v>2280795</v>
       </c>
       <c r="AE4" t="n">
-        <v>883761202</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
-        <v>1492388</v>
-      </c>
+        <v>822930223</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>7563368</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>49735352</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>101723691</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>818758</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>568881</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>567852</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>12691380</v>
+      </c>
       <c r="AL4" t="n">
-        <v>49166471</v>
+        <v>87645701</v>
       </c>
       <c r="AM4" t="n">
-        <v>1919430283</v>
+        <v>1790893283</v>
       </c>
       <c r="AN4" t="n">
-        <v>541462331</v>
+        <v>630589859</v>
       </c>
       <c r="AO4" t="n">
-        <v>4995898</v>
+        <v>4208414</v>
       </c>
       <c r="AP4" t="n">
-        <v>4995898</v>
+        <v>4208414</v>
       </c>
       <c r="AQ4" t="n">
-        <v>536466433</v>
+        <v>626381445</v>
       </c>
       <c r="AR4" t="n">
-        <v>-499566570</v>
+        <v>-544667547</v>
       </c>
       <c r="AS4" t="n">
-        <v>1036033003</v>
+        <v>1171048992</v>
       </c>
       <c r="AT4" t="n">
-        <v>75569152</v>
+        <v>197330308</v>
       </c>
       <c r="AU4" t="n">
-        <v>47694258</v>
+        <v>47223106</v>
       </c>
       <c r="AV4" t="n">
-        <v>534369413</v>
+        <v>545322135</v>
       </c>
       <c r="AW4" t="n">
-        <v>365135455</v>
+        <v>367908718</v>
       </c>
       <c r="AX4" t="n">
         <v>13264725</v>
@@ -2208,56 +2152,62 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1377967952</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
+        <v>1160303424</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>26212564</v>
+      </c>
       <c r="BB4" t="n">
-        <v>939782509</v>
+        <v>780814766</v>
       </c>
       <c r="BC4" t="n">
-        <v>-74007285</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
+        <v>-21435706</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>13185518</v>
+      </c>
       <c r="BE4" t="n">
-        <v>125779426</v>
+        <v>196060064</v>
       </c>
       <c r="BF4" t="n">
-        <v>49473576</v>
+        <v>24179061</v>
       </c>
       <c r="BG4" t="n">
-        <v>838536792</v>
+        <v>568825829</v>
       </c>
       <c r="BH4" t="n">
-        <v>15510172</v>
+        <v>617478</v>
       </c>
       <c r="BI4" t="n">
-        <v>352242535</v>
+        <v>326862117</v>
       </c>
       <c r="BJ4" t="n">
         <v>-9926480</v>
       </c>
       <c r="BK4" t="n">
-        <v>362169015</v>
+        <v>336788597</v>
       </c>
       <c r="BL4" t="n">
-        <v>70432736</v>
+        <v>25796499</v>
       </c>
       <c r="BM4" t="n">
-        <v>2100765</v>
+        <v>1997328</v>
       </c>
       <c r="BN4" t="n">
-        <v>68331971</v>
+        <v>23799171</v>
       </c>
       <c r="BO4" t="n">
-        <v>180000</v>
+        <v>565497</v>
       </c>
       <c r="BP4" t="n">
-        <v>68151971</v>
-      </c>
+        <v>23799171</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="B5" t="n">
         <v>50800000</v>
@@ -2266,43 +2216,43 @@
         <v>50800000</v>
       </c>
       <c r="D5" t="n">
-        <v>310638161</v>
+        <v>779037044</v>
       </c>
       <c r="E5" t="n">
-        <v>519798007</v>
+        <v>878260825</v>
       </c>
       <c r="F5" t="n">
-        <v>757424513</v>
+        <v>585812560</v>
       </c>
       <c r="G5" t="n">
-        <v>1255331150</v>
+        <v>1439137096</v>
       </c>
       <c r="H5" t="n">
-        <v>507099192</v>
+        <v>266297093</v>
       </c>
       <c r="I5" t="n">
-        <v>757424513</v>
+        <v>585812560</v>
       </c>
       <c r="J5" t="n">
-        <v>27798007</v>
+        <v>28204976</v>
       </c>
       <c r="K5" t="n">
-        <v>763331150</v>
+        <v>589081247</v>
       </c>
       <c r="L5" t="n">
-        <v>775831150</v>
+        <v>696259288</v>
       </c>
       <c r="M5" t="n">
-        <v>904697398</v>
+        <v>690965614</v>
       </c>
       <c r="N5" t="n">
-        <v>141366248</v>
+        <v>101884367</v>
       </c>
       <c r="O5" t="n">
-        <v>763331150</v>
+        <v>589081247</v>
       </c>
       <c r="P5" t="n">
-        <v>166133090</v>
+        <v>81081247</v>
       </c>
       <c r="Q5" t="n">
         <v>508000000</v>
@@ -2311,89 +2261,93 @@
         <v>508000000</v>
       </c>
       <c r="S5" t="n">
-        <v>691722986</v>
+        <v>1093545933</v>
       </c>
       <c r="T5" t="n">
-        <v>83034095</v>
+        <v>190872900</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>33624375</v>
+        <v>45481000</v>
       </c>
       <c r="W5" t="n">
-        <v>37710625</v>
+        <v>131935623</v>
       </c>
       <c r="X5" t="n">
-        <v>25210625</v>
+        <v>24757582</v>
       </c>
       <c r="Y5" t="n">
-        <v>12500000</v>
+        <v>107178041</v>
       </c>
       <c r="Z5" t="n">
-        <v>11699095</v>
+        <v>13456277</v>
       </c>
       <c r="AA5" t="n">
-        <v>608688891</v>
+        <v>902673033</v>
       </c>
       <c r="AB5" t="n">
-        <v>30977961</v>
+        <v>16653621</v>
       </c>
       <c r="AC5" t="n">
-        <v>482087382</v>
+        <v>746325202</v>
       </c>
       <c r="AD5" t="n">
-        <v>2587382</v>
+        <v>3447394</v>
       </c>
       <c r="AE5" t="n">
-        <v>479500000</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>5807780</v>
-      </c>
+        <v>742877808</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>29339871</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>50945965</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>95967155</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>818759</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>571439</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>567562</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>12109782</v>
+      </c>
       <c r="AL5" t="n">
-        <v>50374526</v>
+        <v>82471052</v>
       </c>
       <c r="AM5" t="n">
-        <v>1596420384</v>
+        <v>1784511547</v>
       </c>
       <c r="AN5" t="n">
-        <v>480632301</v>
+        <v>615541421</v>
       </c>
       <c r="AO5" t="n">
-        <v>5906637</v>
+        <v>3268687</v>
       </c>
       <c r="AP5" t="n">
-        <v>5906637</v>
+        <v>3268687</v>
       </c>
       <c r="AQ5" t="n">
-        <v>474725664</v>
+        <v>612272734</v>
       </c>
       <c r="AR5" t="n">
-        <v>-454288611</v>
+        <v>-584087963</v>
       </c>
       <c r="AS5" t="n">
-        <v>929014275</v>
+        <v>1196360697</v>
       </c>
       <c r="AT5" t="n">
-        <v>31174844</v>
+        <v>197464624</v>
       </c>
       <c r="AU5" t="n">
-        <v>47799278</v>
+        <v>46636180</v>
       </c>
       <c r="AV5" t="n">
-        <v>491414184</v>
+        <v>567019647</v>
       </c>
       <c r="AW5" t="n">
-        <v>345361244</v>
+        <v>371975521</v>
       </c>
       <c r="AX5" t="n">
         <v>13264725</v>
@@ -2402,51 +2356,261 @@
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1115788083</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
+        <v>1168970126</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>15523871</v>
+      </c>
       <c r="BB5" t="n">
-        <v>624734835</v>
+        <v>679773657</v>
       </c>
       <c r="BC5" t="n">
-        <v>-20874225</v>
-      </c>
-      <c r="BD5" t="inlineStr"/>
+        <v>-16707252</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>25455313</v>
+      </c>
       <c r="BE5" t="n">
-        <v>181927907</v>
+        <v>278312192</v>
       </c>
       <c r="BF5" t="n">
-        <v>47781053</v>
+        <v>29307969</v>
       </c>
       <c r="BG5" t="n">
-        <v>415900100</v>
+        <v>363405435</v>
       </c>
       <c r="BH5" t="n">
-        <v>33414480</v>
+        <v>698221</v>
       </c>
       <c r="BI5" t="n">
-        <v>275064805</v>
+        <v>400865251</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-13311688</v>
+        <v>-9926480</v>
       </c>
       <c r="BK5" t="n">
-        <v>288376493</v>
+        <v>410791731</v>
       </c>
       <c r="BL5" t="n">
-        <v>182573963</v>
+        <v>72109126</v>
       </c>
       <c r="BM5" t="n">
-        <v>1212124</v>
+        <v>1090321</v>
       </c>
       <c r="BN5" t="n">
-        <v>181361839</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>110000000</v>
-      </c>
+        <v>71018805</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="n">
-        <v>71361839</v>
+        <v>71018805</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>-1159235</v>
+      </c>
+      <c r="BR5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>50800000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>50800000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>778595273</v>
+      </c>
+      <c r="E6" t="n">
+        <v>836875279</v>
+      </c>
+      <c r="F6" t="n">
+        <v>618285549</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1433943286</v>
+      </c>
+      <c r="H6" t="n">
+        <v>330891612</v>
+      </c>
+      <c r="I6" t="n">
+        <v>618285549</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24756552</v>
+      </c>
+      <c r="K6" t="n">
+        <v>621824559</v>
+      </c>
+      <c r="L6" t="n">
+        <v>749972768</v>
+      </c>
+      <c r="M6" t="n">
+        <v>719873964</v>
+      </c>
+      <c r="N6" t="n">
+        <v>98049405</v>
+      </c>
+      <c r="O6" t="n">
+        <v>621824559</v>
+      </c>
+      <c r="P6" t="n">
+        <v>113824559</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>508000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>508000000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1045189965</v>
+      </c>
+      <c r="T6" t="n">
+        <v>220274170</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>53253777</v>
+      </c>
+      <c r="W6" t="n">
+        <v>151061305</v>
+      </c>
+      <c r="X6" t="n">
+        <v>22913096</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>128148209</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>15959088</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>824915795</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8257153</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>685813974</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1843456</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>683970518</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>27442860</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>95430397</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3623868</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>567401</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>14822646</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>76416482</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1765063929</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>609256522</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3539010</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3539010</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>605717511</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-626924604</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1232642115</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>30579767</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>44917670</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>674291428</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>469588525</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13264725</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1155807407</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>17862815</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>691527405</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>-10244566</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>29837686</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>260014404</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>25309721</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>386610160</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>421200</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>412037652</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-9926480</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>421964132</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>33958335</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>434881</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>33523454</v>
+      </c>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="n">
+        <v>33523454</v>
+      </c>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2460,7 +2624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2667,494 +2831,619 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45565</v>
+        <v>44469</v>
       </c>
       <c r="B2" t="n">
-        <v>160623818</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-3323069694</v>
-      </c>
+        <v>238488107</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>3269975729</v>
+        <v>62246599</v>
       </c>
       <c r="E2" t="n">
-        <v>-26932478</v>
+        <v>-41288757</v>
       </c>
       <c r="F2" t="n">
-        <v>71018805</v>
+        <v>181361839</v>
       </c>
       <c r="G2" t="n">
-        <v>23799171</v>
+        <v>18456920</v>
       </c>
       <c r="H2" t="n">
-        <v>47219634</v>
+        <v>162904919</v>
       </c>
       <c r="I2" t="n">
-        <v>-116323840</v>
+        <v>-74913663</v>
       </c>
       <c r="J2" t="n">
-        <v>-58935709</v>
+        <v>-10016046</v>
       </c>
       <c r="K2" t="n">
-        <v>-53093965</v>
+        <v>62246599</v>
       </c>
       <c r="L2" t="n">
-        <v>-53093965</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-3323069694</v>
-      </c>
+        <v>62246599</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>3269975729</v>
+        <v>62246599</v>
       </c>
       <c r="O2" t="n">
-        <v>-24012822</v>
+        <v>-41958282</v>
       </c>
       <c r="P2" t="n">
-        <v>2918910</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10670226</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-7751316</v>
-      </c>
+        <v>-932878</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-9705</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-9705</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>-26922027</v>
+        <v>-41025404</v>
       </c>
       <c r="V2" t="n">
-        <v>746</v>
+        <v>263353</v>
       </c>
       <c r="W2" t="n">
-        <v>-26922773</v>
+        <v>-41288757</v>
       </c>
       <c r="X2" t="n">
-        <v>187556296</v>
+        <v>279776864</v>
       </c>
       <c r="Y2" t="n">
-        <v>-19440888</v>
+        <v>-14739312</v>
       </c>
       <c r="Z2" t="n">
-        <v>18512711</v>
+        <v>-52779054</v>
       </c>
       <c r="AA2" t="n">
-        <v>-13956112</v>
+        <v>1169944</v>
       </c>
       <c r="AB2" t="n">
-        <v>-4805298</v>
+        <v>-9171821</v>
       </c>
       <c r="AC2" t="n">
-        <v>-5174649</v>
+        <v>6129759</v>
       </c>
       <c r="AD2" t="n">
-        <v>10607950</v>
+        <v>-6496223</v>
       </c>
       <c r="AE2" t="n">
-        <v>105843954</v>
+        <v>-102195624</v>
       </c>
       <c r="AF2" t="n">
-        <v>-74003134</v>
+        <v>57784911</v>
       </c>
       <c r="AG2" t="n">
-        <v>66852034</v>
+        <v>13310210</v>
       </c>
       <c r="AH2" t="n">
-        <v>-549658</v>
+        <v>18497935</v>
       </c>
       <c r="AI2" t="n">
-        <v>48047261</v>
+        <v>45696195</v>
       </c>
       <c r="AJ2" t="n">
-        <v>949432</v>
+        <v>917879</v>
       </c>
       <c r="AK2" t="n">
-        <v>47097829</v>
+        <v>44778316</v>
       </c>
       <c r="AL2" t="n">
-        <v>7194008</v>
+        <v>5351172</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2011903</v>
+        <v>-279246</v>
       </c>
       <c r="AN2" t="n">
-        <v>919</v>
+        <v>-175786</v>
       </c>
       <c r="AO2" t="n">
-        <v>80946297</v>
+        <v>268935112</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45199</v>
+        <v>44834</v>
       </c>
       <c r="B3" t="n">
-        <v>1280143</v>
+        <v>-386169117</v>
       </c>
       <c r="C3" t="n">
-        <v>-4238664825</v>
+        <v>-2205193279</v>
       </c>
       <c r="D3" t="n">
-        <v>4255553437</v>
+        <v>2599454481</v>
       </c>
       <c r="E3" t="n">
-        <v>-137577635</v>
+        <v>-99492068</v>
       </c>
       <c r="F3" t="n">
-        <v>23799171</v>
+        <v>68331971</v>
       </c>
       <c r="G3" t="n">
-        <v>68331971</v>
+        <v>181361839</v>
       </c>
       <c r="H3" t="n">
-        <v>-44532800</v>
+        <v>-113029868</v>
       </c>
       <c r="I3" t="n">
-        <v>-48470208</v>
+        <v>271208488</v>
       </c>
       <c r="J3" t="n">
-        <v>-60387597</v>
+        <v>-16616211</v>
       </c>
       <c r="K3" t="n">
-        <v>16888612</v>
+        <v>394261202</v>
       </c>
       <c r="L3" t="n">
-        <v>16888612</v>
+        <v>394261202</v>
       </c>
       <c r="M3" t="n">
-        <v>-4238664825</v>
+        <v>-2205193279</v>
       </c>
       <c r="N3" t="n">
-        <v>4255553437</v>
+        <v>2599454481</v>
       </c>
       <c r="O3" t="n">
-        <v>-134920370</v>
+        <v>-97561307</v>
       </c>
       <c r="P3" t="n">
-        <v>2002438</v>
+        <v>1886431</v>
       </c>
       <c r="Q3" t="n">
-        <v>20696985</v>
+        <v>22133942</v>
       </c>
       <c r="R3" t="n">
-        <v>-18694547</v>
+        <v>-20247511</v>
       </c>
       <c r="S3" t="n">
-        <v>-154019</v>
+        <v>-7500</v>
       </c>
       <c r="T3" t="n">
-        <v>-154019</v>
+        <v>-7500</v>
       </c>
       <c r="U3" t="n">
-        <v>-136768789</v>
+        <v>-99440238</v>
       </c>
       <c r="V3" t="n">
-        <v>654827</v>
+        <v>44330</v>
       </c>
       <c r="W3" t="n">
-        <v>-137423616</v>
+        <v>-99484568</v>
       </c>
       <c r="X3" t="n">
-        <v>138857778</v>
+        <v>-286677049</v>
       </c>
       <c r="Y3" t="n">
-        <v>-8445801</v>
+        <v>-15062429</v>
       </c>
       <c r="Z3" t="n">
-        <v>242303412</v>
+        <v>-388982123</v>
       </c>
       <c r="AA3" t="n">
-        <v>-14782948</v>
+        <v>36227839</v>
       </c>
       <c r="AB3" t="n">
-        <v>-6992739</v>
+        <v>2548089</v>
       </c>
       <c r="AC3" t="n">
-        <v>38479230</v>
+        <v>-1745230</v>
       </c>
       <c r="AD3" t="n">
-        <v>-11319870</v>
+        <v>17904308</v>
       </c>
       <c r="AE3" t="n">
-        <v>211539321</v>
+        <v>-368180734</v>
       </c>
       <c r="AF3" t="n">
-        <v>25380418</v>
+        <v>-75736395</v>
       </c>
       <c r="AG3" t="n">
-        <v>68955249</v>
+        <v>26075992</v>
       </c>
       <c r="AH3" t="n">
-        <v>-54582065</v>
+        <v>-8551507</v>
       </c>
       <c r="AI3" t="n">
-        <v>48979733</v>
+        <v>47025307</v>
       </c>
       <c r="AJ3" t="n">
-        <v>941503</v>
+        <v>918239</v>
       </c>
       <c r="AK3" t="n">
-        <v>48038230</v>
+        <v>46107068</v>
       </c>
       <c r="AL3" t="n">
-        <v>6745988</v>
+        <v>5716468</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1899001</v>
+        <v>-2775072</v>
       </c>
       <c r="AN3" t="n">
-        <v>-185636</v>
+        <v>12384</v>
       </c>
       <c r="AO3" t="n">
-        <v>-160586461</v>
+        <v>-3646320</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44834</v>
+        <v>45199</v>
       </c>
       <c r="B4" t="n">
-        <v>-386169117</v>
+        <v>1280143</v>
       </c>
       <c r="C4" t="n">
-        <v>-2205193279</v>
+        <v>-4238664825</v>
       </c>
       <c r="D4" t="n">
-        <v>2599454481</v>
+        <v>4255553437</v>
       </c>
       <c r="E4" t="n">
-        <v>-99492068</v>
+        <v>-137577635</v>
       </c>
       <c r="F4" t="n">
+        <v>23799171</v>
+      </c>
+      <c r="G4" t="n">
         <v>68331971</v>
       </c>
-      <c r="G4" t="n">
-        <v>181361839</v>
-      </c>
       <c r="H4" t="n">
-        <v>-113029868</v>
+        <v>-44532800</v>
       </c>
       <c r="I4" t="n">
-        <v>271208488</v>
+        <v>-48470208</v>
       </c>
       <c r="J4" t="n">
-        <v>-16616211</v>
+        <v>-60387597</v>
       </c>
       <c r="K4" t="n">
-        <v>394261202</v>
+        <v>16888612</v>
       </c>
       <c r="L4" t="n">
-        <v>394261202</v>
+        <v>16888612</v>
       </c>
       <c r="M4" t="n">
-        <v>-2205193279</v>
+        <v>-4238664825</v>
       </c>
       <c r="N4" t="n">
-        <v>2599454481</v>
+        <v>4255553437</v>
       </c>
       <c r="O4" t="n">
-        <v>-97561307</v>
+        <v>-134920370</v>
       </c>
       <c r="P4" t="n">
-        <v>1886431</v>
+        <v>2002438</v>
       </c>
       <c r="Q4" t="n">
-        <v>22133942</v>
+        <v>20696985</v>
       </c>
       <c r="R4" t="n">
-        <v>-20247511</v>
+        <v>-18694547</v>
       </c>
       <c r="S4" t="n">
-        <v>-7500</v>
+        <v>-154019</v>
       </c>
       <c r="T4" t="n">
-        <v>-7500</v>
+        <v>-154019</v>
       </c>
       <c r="U4" t="n">
-        <v>-99440238</v>
+        <v>-136768789</v>
       </c>
       <c r="V4" t="n">
-        <v>44330</v>
+        <v>654827</v>
       </c>
       <c r="W4" t="n">
-        <v>-99484568</v>
+        <v>-137423616</v>
       </c>
       <c r="X4" t="n">
-        <v>-286677049</v>
+        <v>138857778</v>
       </c>
       <c r="Y4" t="n">
-        <v>-15062429</v>
+        <v>-8445801</v>
       </c>
       <c r="Z4" t="n">
-        <v>-388982123</v>
+        <v>242303412</v>
       </c>
       <c r="AA4" t="n">
-        <v>36227839</v>
+        <v>-14782948</v>
       </c>
       <c r="AB4" t="n">
-        <v>2548089</v>
+        <v>-6992739</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1745230</v>
+        <v>38479230</v>
       </c>
       <c r="AD4" t="n">
-        <v>17904308</v>
+        <v>-11319870</v>
       </c>
       <c r="AE4" t="n">
-        <v>-368180734</v>
+        <v>211539321</v>
       </c>
       <c r="AF4" t="n">
-        <v>-75736395</v>
+        <v>25380418</v>
       </c>
       <c r="AG4" t="n">
-        <v>26075992</v>
+        <v>68955249</v>
       </c>
       <c r="AH4" t="n">
-        <v>-8551507</v>
+        <v>-54582065</v>
       </c>
       <c r="AI4" t="n">
-        <v>47025307</v>
+        <v>48979733</v>
       </c>
       <c r="AJ4" t="n">
-        <v>918239</v>
+        <v>941503</v>
       </c>
       <c r="AK4" t="n">
-        <v>46107068</v>
+        <v>48038230</v>
       </c>
       <c r="AL4" t="n">
-        <v>5716468</v>
+        <v>6745988</v>
       </c>
       <c r="AM4" t="n">
-        <v>-2775072</v>
+        <v>-1899001</v>
       </c>
       <c r="AN4" t="n">
-        <v>12384</v>
+        <v>-185636</v>
       </c>
       <c r="AO4" t="n">
-        <v>-3646320</v>
+        <v>-160586461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44469</v>
+        <v>45565</v>
       </c>
       <c r="B5" t="n">
-        <v>238488107</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>160623818</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-3323069694</v>
+      </c>
       <c r="D5" t="n">
-        <v>62246599</v>
+        <v>3269975729</v>
       </c>
       <c r="E5" t="n">
-        <v>-41288757</v>
+        <v>-26932478</v>
       </c>
       <c r="F5" t="n">
-        <v>181361839</v>
+        <v>71018805</v>
       </c>
       <c r="G5" t="n">
-        <v>18456920</v>
+        <v>23799171</v>
       </c>
       <c r="H5" t="n">
-        <v>162904919</v>
+        <v>47219634</v>
       </c>
       <c r="I5" t="n">
-        <v>-74913663</v>
+        <v>-116323840</v>
       </c>
       <c r="J5" t="n">
-        <v>-10016046</v>
+        <v>-58935709</v>
       </c>
       <c r="K5" t="n">
-        <v>62246599</v>
+        <v>-53093965</v>
       </c>
       <c r="L5" t="n">
-        <v>62246599</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-53093965</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-3323069694</v>
+      </c>
       <c r="N5" t="n">
-        <v>62246599</v>
+        <v>3269975729</v>
       </c>
       <c r="O5" t="n">
-        <v>-41958282</v>
+        <v>-24012822</v>
       </c>
       <c r="P5" t="n">
-        <v>-932878</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>2918910</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10670226</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-7751316</v>
+      </c>
       <c r="S5" t="n">
+        <v>-9705</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-9705</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-26922027</v>
+      </c>
+      <c r="V5" t="n">
+        <v>746</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-26922773</v>
+      </c>
+      <c r="X5" t="n">
+        <v>187556296</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-19440888</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>18512711</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-13956112</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-4805298</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-5174649</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10607950</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>105843954</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-74003134</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>66852034</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-549658</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>48047261</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>949432</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>47097829</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>7194008</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-2011903</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>919</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>80946297</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84366828</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-3432212511</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3394275389</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-38912244</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33523454</v>
+      </c>
+      <c r="G6" t="n">
+        <v>71018805</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-37495351</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-123198300</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-56007470</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-37937122</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-37937122</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-3432212511</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3394275389</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-37576123</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1336121</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5477316</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-4141195</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-437500</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-437500</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-38474744</v>
+      </c>
+      <c r="V6" t="n">
         <v>0</v>
       </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>-41025404</v>
-      </c>
-      <c r="V5" t="n">
-        <v>263353</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-41288757</v>
-      </c>
-      <c r="X5" t="n">
-        <v>279776864</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>-14739312</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-52779054</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1169944</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>-9171821</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>6129759</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-6496223</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-102195624</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>57784911</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13310210</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>18497935</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>45696195</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>917879</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>44778316</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>5351172</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-279246</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-175786</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>268935112</v>
+      <c r="W6" t="n">
+        <v>-38474744</v>
+      </c>
+      <c r="X6" t="n">
+        <v>123279072</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-8474859</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-29634206</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-8225853</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3171603</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-6054570</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-2061923</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-5291062</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-11172401</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>58907358</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-2288505</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>47463212</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>964917</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>46498295</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>9200242</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-680681</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>644</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55994958</v>
       </c>
     </row>
   </sheetData>
@@ -3168,7 +3457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EK2"/>
+  <dimension ref="A1:EP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3599,280 +3888,305 @@
       </c>
       <c r="CH1" t="inlineStr">
         <is>
+          <t>quickRatio</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>currentRatio</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>returnOnAssets</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>returnOnEquity</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>freeCashflow</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3969,28 +4283,28 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>39.46</v>
+        <v>39.38</v>
       </c>
       <c r="U2" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="V2" t="n">
-        <v>39.04</v>
+        <v>39.4</v>
       </c>
       <c r="W2" t="n">
-        <v>40.18</v>
+        <v>40.48</v>
       </c>
       <c r="X2" t="n">
-        <v>39.46</v>
+        <v>39.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>39.04</v>
+        <v>39.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>40.18</v>
+        <v>40.48</v>
       </c>
       <c r="AB2" t="n">
         <v>0.5</v>
@@ -4002,37 +4316,37 @@
         <v>1741132800</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5495</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.62</v>
+        <v>0.543</v>
       </c>
       <c r="AG2" t="n">
-        <v>42.96703</v>
+        <v>17.188036</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.638298</v>
+        <v>17.114895</v>
       </c>
       <c r="AI2" t="n">
-        <v>284438</v>
+        <v>590836</v>
       </c>
       <c r="AJ2" t="n">
-        <v>284438</v>
+        <v>590836</v>
       </c>
       <c r="AK2" t="n">
-        <v>395323</v>
+        <v>420599</v>
       </c>
       <c r="AL2" t="n">
-        <v>223285</v>
+        <v>340414</v>
       </c>
       <c r="AM2" t="n">
-        <v>223285</v>
+        <v>340414</v>
       </c>
       <c r="AN2" t="n">
-        <v>39.08</v>
+        <v>40.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>38.36</v>
+        <v>40.32</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4041,13 +4355,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1986279936</v>
+        <v>2043176064</v>
       </c>
       <c r="AS2" t="n">
-        <v>2004568000</v>
+        <v>2043176000</v>
       </c>
       <c r="AT2" t="n">
-        <v>26.5</v>
+        <v>27.75</v>
       </c>
       <c r="AU2" t="n">
         <v>43.5</v>
@@ -4059,13 +4373,13 @@
         <v>12.96</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.0423962</v>
+        <v>1.0722549</v>
       </c>
       <c r="AY2" t="n">
-        <v>38.4684</v>
+        <v>39.3432</v>
       </c>
       <c r="AZ2" t="n">
-        <v>36.3876</v>
+        <v>36.738</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -4082,13 +4396,13 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>3000256256</v>
+        <v>3239340544</v>
       </c>
       <c r="BF2" t="n">
         <v>0.06258</v>
       </c>
       <c r="BG2" t="n">
-        <v>36294568</v>
+        <v>36293044</v>
       </c>
       <c r="BH2" t="n">
         <v>50800000</v>
@@ -4097,16 +4411,16 @@
         <v>0.08821999</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.20547001</v>
+        <v>0.20534</v>
       </c>
       <c r="BK2" t="n">
         <v>50800000</v>
       </c>
       <c r="BL2" t="n">
-        <v>12.981</v>
+        <v>13.935</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.0120945</v>
+        <v>2.8862576</v>
       </c>
       <c r="BN2" t="n">
         <v>1759190400</v>
@@ -4121,25 +4435,25 @@
         <v>1.209</v>
       </c>
       <c r="BR2" t="n">
-        <v>119240112</v>
+        <v>119239816</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.91</v>
+        <v>2.34</v>
       </c>
       <c r="BT2" t="n">
         <v>2.35</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.575</v>
+        <v>1.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.821</v>
+        <v>13.829</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.32194304</v>
+        <v>0.42624116</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.2568333</v>
       </c>
       <c r="BY2" t="n">
         <v>0.5</v>
@@ -4153,7 +4467,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>39.1</v>
+        <v>40.22</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -4161,104 +4475,98 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>139451040</v>
+        <v>74551400</v>
       </c>
       <c r="CE2" t="n">
-        <v>2.745</v>
+        <v>1.468</v>
       </c>
       <c r="CF2" t="n">
-        <v>217077536</v>
+        <v>234237760</v>
       </c>
       <c r="CG2" t="n">
-        <v>1056576768</v>
+        <v>1178702208</v>
       </c>
       <c r="CH2" t="n">
-        <v>1905494272</v>
+        <v>0.543</v>
       </c>
       <c r="CI2" t="n">
-        <v>139.706</v>
+        <v>1.324</v>
       </c>
       <c r="CJ2" t="n">
-        <v>37.466</v>
+        <v>1905494784</v>
       </c>
       <c r="CK2" t="n">
-        <v>237956912</v>
+        <v>146.421</v>
       </c>
       <c r="CL2" t="n">
-        <v>-90513928</v>
+        <v>37.51</v>
       </c>
       <c r="CM2" t="n">
+        <v>0.05771</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>0.15548</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>276643072</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-243498192</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>-64107104</v>
+      </c>
+      <c r="CR2" t="n">
         <v>1.209</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CS2" t="n">
         <v>0.026</v>
       </c>
-      <c r="CO2" t="n">
-        <v>0.12488</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.11392</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.09897</v>
-      </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CT2" t="n">
+        <v>0.14518</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.122930005</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.13006</v>
+      </c>
+      <c r="CW2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>1304.SR</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CX2" t="b">
+      <c r="DC2" t="b">
         <v>0</v>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>LOW</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>-0.9123178</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="DC2" t="inlineStr">
-        <is>
-          <t>Al Yamamah Steel Industries Co.</t>
-        </is>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>Al Yamamah Steel Industries Company</t>
         </is>
       </c>
       <c r="DE2" t="b">
@@ -4268,118 +4576,139 @@
         <v>1463900400000</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0.3600006</v>
+        <v>0.8400001499999999</v>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>39.04 - 40.18</t>
+          <t>39.4 - 40.48</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
+          <t>Saudi</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>420599</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>12.470001</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.4493694</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>27.75 - 43.5</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-3.2799988</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.07540226999999999</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>42.624115</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>2.1330628</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>1780402687</v>
-      </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>1781785086</v>
+      </c>
+      <c r="DU2" t="inlineStr">
         <is>
           <t>SAU</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>finmb_5418815</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>Asia/Riyadh</t>
         </is>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
-      <c r="DO2" t="n">
+      <c r="DY2" t="n">
         <v>10800000</v>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>sr_market</t>
         </is>
       </c>
-      <c r="DQ2" t="b">
+      <c r="EA2" t="b">
         <v>0</v>
       </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Saudi</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>395323</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>12.599998</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.47547165</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>26.5 - 43.5</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-4.4000015</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.10114946</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>32.194305</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="EA2" t="n">
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="ED2" t="n">
         <v>2.35</v>
       </c>
-      <c r="EB2" t="n">
-        <v>0.6315994</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.016418656</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>2.7123985</v>
-      </c>
       <c r="EE2" t="n">
-        <v>0.07454184</v>
+        <v>0.87680054</v>
       </c>
       <c r="EF2" t="n">
+        <v>0.022285948</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>3.4820023</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.09477931000000001</v>
+      </c>
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>Al-Yamamah Steel Industries Company</t>
         </is>
       </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
+      <c r="EL2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="EM2" t="b">
         <v>0</v>
       </c>
-      <c r="EK2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>Al Yamamah Steel Industries Co.</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>Al Yamamah Steel Industries Company</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
